--- a/pensum/ok02/LOM_Ovingsark_Okonomistyring_kap02_Kostnadsbegreper_NY.xlsx
+++ b/pensum/ok02/LOM_Ovingsark_Okonomistyring_kap02_Kostnadsbegreper_NY.xlsx
@@ -1411,11 +1411,11 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Varekostnad underentreprenør</t>
+          <t>Varekostnad innleide montører</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>3660000</v>
+        <v>400000</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Innleid hjelp, bestilt per prosjekt.</t>
+          <t>Innleide montører i topper, bestilt per prosjekt.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>5180000</v>
+        <v>8440000</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>

--- a/pensum/ok02/LOM_Ovingsark_Okonomistyring_kap02_Kostnadsbegreper_NY.xlsx
+++ b/pensum/ok02/LOM_Ovingsark_Okonomistyring_kap02_Kostnadsbegreper_NY.xlsx
@@ -320,7 +320,7 @@
     <t xml:space="preserve">Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Utgift, utbetaling og kostnad</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">Prøv dette: sett kredittiden i B7 til 0. Da — og bare da — er utgift og utbetaling det samme. Legg merke til at varekostnaden ikke rører seg.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 2.2.1. Tallene er Nordlys Elektro AS, mars til mai 2026, med Polarlys Elektro Grossist AS som leverandør.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 2.2.1. Tallene er Nordlys Elektro AS, mars til mai 2026, med Polarlys Elektro Grossist AS som leverandør.</t>
   </si>
   <si>
     <t xml:space="preserve">Fast eller variabel?</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">Prøv dette: sett F på en av de variable postene og se hva som skjer med prosenten — og med driftsresultatet. Sorteringen er ikke en formalitet; den avgjør hele kalkylen i kapittel 5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 2.2.2. Tallene er Nordlys Elektro AS 2026.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 2.2.2. Tallene er Nordlys Elektro AS 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Hva skjer per enhet når aktiviteten endres?</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">Merk: arket forutsetter at de variable kostnadene er proporsjonale med aktiviteten. Det holder så lenge jobbmiksen er den samme. Følger materiellet jobben og ikke timen, blir det en forenkling — en ærlig en, men en forenkling.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 2.2.2 og figurene 2.2 til 2.5. Tallene er Nordlys Elektro AS 2026.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 2.2.2 og figurene 2.2 til 2.5. Tallene er Nordlys Elektro AS 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Avskrivning: lineær metode mot saldometoden</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">Merk: avskrivning er ikke en utbetaling. Pengene forsvant da bilen ble kjøpt — kolonnene fordeler bare kostnaden over årene bilen brukes. Derfor er avskrivningen en fast kostnad: den følger tida, ikke kilometerne.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 2.4.3. Saldosats: skatteetaten.no. Bilen er servicebilen Nordlys kjøpte i 2026.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 2.4.3. Saldosats: skatteetaten.no. Bilen er servicebilen Nordlys kjøpte i 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Hva koster en ansatt?</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">Er faktureringsgraden lavere enn Nordlys sin?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 2.2.2 og 2.3.1, med støtte i kap. 5 om timepris og kap. 8 om nullpunkt. Tallene er Nordlys Elektro AS 2026. Vestli Elektro AS er konstruert for øvingen, med samme kostnadsstruktur som Nordlys.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 2.2.2 og 2.3.1, med støtte i kap. 5 om timepris og kap. 8 om nullpunkt. Tallene er Nordlys Elektro AS 2026. Vestli Elektro AS er konstruert for øvingen, med samme kostnadsstruktur som Nordlys.</t>
   </si>
 </sst>
 </file>
